--- a/rmonize/data_dictionary/DD_CARLA_P2.xlsx
+++ b/rmonize/data_dictionary/DD_CARLA_P2.xlsx
@@ -1033,7 +1033,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>integer</t>
         </is>
       </c>
     </row>
